--- a/老虎机数学专题-倍率百搭.xlsx
+++ b/老虎机数学专题-倍率百搭.xlsx
@@ -4292,6 +4292,9 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Z98" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6718,5 +6721,8 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L129" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/老虎机数学专题-倍率百搭.xlsx
+++ b/老虎机数学专题-倍率百搭.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="倍率百搭 含与不含WILD→RTP汇总" sheetId="8" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="130">
   <si>
     <t>倍率百搭 Wild Multiplier（原文数据版）</t>
   </si>
@@ -1162,7 +1162,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1226,6 +1226,32 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2276,1986 +2302,1986 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:10">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="23" t="s">
+      <c r="B17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="23" t="s">
+      <c r="A18" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:10">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="23" t="s">
+      <c r="B19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:10">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="23" t="s">
+      <c r="B20" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:10">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="23" t="s">
+      <c r="B21" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:10">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="23" t="s">
+      <c r="B22" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="23" t="s">
+      <c r="A23" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:10">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="23" t="s">
+      <c r="B24" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:10">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="23" t="s">
+      <c r="B25" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:10">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="23" t="s">
+      <c r="B26" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="23" t="s">
+      <c r="A27" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:10">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28" s="23" t="s">
+      <c r="B28" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="16.5" spans="1:10">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I29" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J29" s="23" t="s">
+      <c r="B29" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="16.5" spans="1:10">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G30" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I30" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J30" s="23" t="s">
+      <c r="B30" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I30" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J30" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:10">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J31" s="23" t="s">
+      <c r="B31" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H32" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I32" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J32" s="23" t="s">
+      <c r="A32" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H32" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I32" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:10">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G33" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33" s="23" t="s">
+      <c r="B33" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E33" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H33" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:10">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J34" s="23" t="s">
+      <c r="B34" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D34" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E34" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H34" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:10">
-      <c r="A35" s="27" t="s">
+      <c r="A35" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G35" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I35" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J35" s="23" t="s">
+      <c r="B35" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E35" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:10">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F36" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J36" s="23" t="s">
+      <c r="B36" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H36" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:10">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H37" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I37" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J37" s="23" t="s">
+      <c r="B37" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E37" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H37" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I37" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:10">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H38" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I38" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J38" s="23" t="s">
+      <c r="B38" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E38" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I38" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:10">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H39" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J39" s="23" t="s">
+      <c r="B39" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D39" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E39" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H39" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I39" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:10">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B40" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H40" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I40" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J40" s="23" t="s">
+      <c r="B40" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E40" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H40" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I40" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:10">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G41" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H41" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I41" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J41" s="23" t="s">
+      <c r="B41" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E41" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H41" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I41" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B42" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F42" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I42" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J42" s="23" t="s">
+      <c r="A42" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E42" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I42" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="43" ht="16.5" spans="1:10">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="B43" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F43" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H43" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I43" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J43" s="23" t="s">
+      <c r="B43" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H43" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I43" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:10">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C44" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F44" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I44" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J44" s="23" t="s">
+      <c r="B44" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E44" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I44" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:10">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B45" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C45" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F45" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I45" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45" s="23" t="s">
+      <c r="B45" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E45" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F45" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I45" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:10">
-      <c r="A46" s="27" t="s">
+      <c r="A46" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F46" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H46" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I46" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J46" s="23" t="s">
+      <c r="B46" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H46" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I46" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J46" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:10">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H47" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I47" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="23" t="s">
+      <c r="B47" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E47" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F47" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H47" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I47" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:10">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="B48" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D48" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E48" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I48" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J48" s="23" t="s">
+      <c r="B48" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D48" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E48" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I48" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J48" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1" spans="1:10">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="30" t="s">
+      <c r="B49" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G49" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H49" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I49" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49" s="23" t="s">
+      <c r="C49" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E49" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F49" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H49" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I49" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J49" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="14.5" spans="1:10">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="32" t="s">
+      <c r="B50" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="C50" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F50" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J50" s="23" t="s">
+      <c r="C50" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F50" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I50" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J50" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="51" ht="14.5" spans="1:10">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="B51" s="32" t="s">
+      <c r="B51" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C51" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F51" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G51" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H51" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I51" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51" s="23" t="s">
+      <c r="C51" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E51" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F51" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I51" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B52" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E52" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F52" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G52" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I52" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J52" s="23" t="s">
+      <c r="A52" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E52" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F52" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I52" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:10">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="B53" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E53" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F53" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G53" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I53" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J53" s="23" t="s">
+      <c r="B53" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I53" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B54" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F54" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H54" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I54" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J54" s="23" t="s">
+      <c r="A54" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E54" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I54" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J54" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:10">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="B55" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E55" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F55" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G55" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H55" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I55" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J55" s="23" t="s">
+      <c r="B55" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F55" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I55" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J55" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:10">
-      <c r="A56" s="27" t="s">
+      <c r="A56" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="B56" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D56" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F56" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G56" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H56" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I56" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J56" s="23" t="s">
+      <c r="B56" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F56" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G56" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H56" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I56" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J56" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:10">
-      <c r="A57" s="28" t="s">
+      <c r="A57" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B57" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F57" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I57" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J57" s="23" t="s">
+      <c r="B57" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F57" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I57" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:10">
-      <c r="A58" s="28" t="s">
+      <c r="A58" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B58" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E58" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F58" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H58" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I58" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J58" s="23" t="s">
+      <c r="B58" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H58" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I58" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J58" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:10">
-      <c r="A59" s="26" t="s">
+      <c r="A59" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="B59" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C59" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E59" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H59" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I59" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J59" s="23" t="s">
+      <c r="B59" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E59" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F59" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H59" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I59" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J59" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B60" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C60" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E60" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F60" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I60" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J60" s="23" t="s">
+      <c r="A60" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B60" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D60" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F60" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I60" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J60" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:10">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="B61" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C61" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E61" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H61" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I61" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J61" s="23" t="s">
+      <c r="B61" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D61" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E61" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F61" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I61" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="62" ht="16.5" spans="1:10">
-      <c r="A62" s="27" t="s">
+      <c r="A62" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="B62" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C62" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E62" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I62" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J62" s="23" t="s">
+      <c r="B62" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E62" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F62" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H62" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I62" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J62" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:10">
-      <c r="A63" s="28" t="s">
+      <c r="A63" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="B63" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C63" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E63" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G63" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H63" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I63" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J63" s="23" t="s">
+      <c r="B63" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F63" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H63" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I63" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:10">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="B64" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C64" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D64" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E64" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F64" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G64" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H64" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I64" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J64" s="23" t="s">
+      <c r="B64" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E64" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F64" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H64" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I64" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J64" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="65" ht="16.5" spans="1:10">
-      <c r="A65" s="27" t="s">
+      <c r="A65" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="B65" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E65" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F65" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G65" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H65" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I65" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J65" s="23" t="s">
+      <c r="B65" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F65" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H65" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I65" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="66" ht="16.5" spans="1:10">
-      <c r="A66" s="27" t="s">
+      <c r="A66" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="B66" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D66" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E66" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G66" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H66" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I66" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J66" s="23" t="s">
+      <c r="B66" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E66" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H66" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I66" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J66" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:10">
-      <c r="A67" s="26" t="s">
+      <c r="A67" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="B67" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C67" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D67" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E67" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G67" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H67" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I67" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J67" s="23" t="s">
+      <c r="B67" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H67" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I67" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J67" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B68" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D68" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E68" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F68" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G68" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H68" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I68" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J68" s="23" t="s">
+      <c r="A68" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E68" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F68" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G68" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H68" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I68" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J68" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" spans="1:10">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="30" t="s">
+      <c r="B69" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="C69" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D69" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E69" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F69" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G69" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H69" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I69" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J69" s="23" t="s">
+      <c r="C69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I69" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J69" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="70" ht="14.5" spans="1:10">
-      <c r="A70" s="31" t="s">
+      <c r="A70" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="32" t="s">
+      <c r="B70" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="C70" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E70" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F70" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G70" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H70" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I70" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J70" s="23" t="s">
+      <c r="C70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I70" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J70" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="71" ht="14.5" spans="1:10">
-      <c r="A71" s="31" t="s">
+      <c r="A71" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="B71" s="32" t="s">
+      <c r="B71" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C71" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E71" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F71" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G71" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H71" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I71" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J71" s="23" t="s">
+      <c r="C71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I71" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J71" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="72" ht="14.5" spans="1:10">
-      <c r="A72" s="31" t="s">
+      <c r="A72" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="32" t="s">
+      <c r="B72" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="C72" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E72" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F72" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G72" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H72" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I72" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J72" s="23" t="s">
+      <c r="C72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I72" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J72" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="73" ht="14.5" spans="1:10">
-      <c r="A73" s="31" t="s">
+      <c r="A73" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="B73" s="32" t="s">
+      <c r="B73" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="C73" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D73" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E73" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G73" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H73" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I73" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J73" s="23" t="s">
+      <c r="C73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I73" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J73" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="74" ht="14.5" spans="1:10">
-      <c r="A74" s="31" t="s">
+      <c r="A74" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="32" t="s">
+      <c r="B74" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="C74" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D74" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E74" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F74" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G74" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H74" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I74" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J74" s="23" t="s">
+      <c r="C74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I74" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J74" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="75" ht="14.5" spans="1:10">
-      <c r="A75" s="31" t="s">
+      <c r="A75" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="B75" s="32" t="s">
+      <c r="B75" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D75" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E75" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F75" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G75" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H75" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I75" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J75" s="23" t="s">
+      <c r="C75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I75" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J75" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="76" ht="14.5" spans="1:10">
-      <c r="A76" s="31" t="s">
+      <c r="A76" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="B76" s="32" t="s">
+      <c r="B76" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="C76" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D76" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E76" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F76" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G76" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H76" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I76" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J76" s="23" t="s">
+      <c r="C76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I76" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J76" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="77" ht="14.5" spans="1:10">
-      <c r="A77" s="31" t="s">
+      <c r="A77" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="32" t="s">
+      <c r="B77" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="C77" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D77" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E77" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F77" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G77" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H77" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I77" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J77" s="23" t="s">
+      <c r="C77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I77" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J77" s="34" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="78" ht="14.5" spans="1:10">
-      <c r="A78" s="31" t="s">
+      <c r="A78" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="B78" s="32" t="s">
+      <c r="B78" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="C78" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D78" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E78" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F78" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G78" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="H78" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I78" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="J78" s="23" t="s">
+      <c r="C78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="E78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="H78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="I78" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="J78" s="34" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4494,8 +4520,8 @@
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>86</v>
+      <c r="A10" s="44">
+        <v>10</v>
       </c>
       <c r="B10" s="8">
         <v>5</v>
@@ -4717,8 +4743,8 @@
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="4" t="s">
-        <v>86</v>
+      <c r="A21" s="44">
+        <v>10</v>
       </c>
       <c r="B21" s="8">
         <v>1</v>
@@ -4973,8 +4999,8 @@
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:6">
-      <c r="A33" s="4" t="s">
-        <v>86</v>
+      <c r="A33" s="44">
+        <v>10</v>
       </c>
       <c r="B33" s="4">
         <f>B10*C10*D10</f>
@@ -5214,8 +5240,8 @@
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:6">
-      <c r="A44" s="4" t="s">
-        <v>86</v>
+      <c r="A44" s="44">
+        <v>10</v>
       </c>
       <c r="B44" s="4">
         <f>(B10+B$5)*(C10+C$5)*(D10+D$5)-B33</f>
@@ -6307,8 +6333,8 @@
       </c>
     </row>
     <row r="92" ht="16.5" spans="1:6">
-      <c r="A92" s="4" t="s">
-        <v>86</v>
+      <c r="A92" s="44">
+        <v>10</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>114</v>
@@ -6331,8 +6357,8 @@
       </c>
     </row>
     <row r="93" ht="16.5" spans="1:6">
-      <c r="A93" s="4" t="s">
-        <v>86</v>
+      <c r="A93" s="44">
+        <v>10</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>115</v>
@@ -6355,8 +6381,8 @@
       </c>
     </row>
     <row r="94" ht="16.5" spans="1:6">
-      <c r="A94" s="4" t="s">
-        <v>86</v>
+      <c r="A94" s="44">
+        <v>10</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>116</v>
@@ -6379,8 +6405,8 @@
       </c>
     </row>
     <row r="95" ht="16.5" spans="1:6">
-      <c r="A95" s="4" t="s">
-        <v>86</v>
+      <c r="A95" s="44">
+        <v>10</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>117</v>
@@ -6403,8 +6429,8 @@
       </c>
     </row>
     <row r="96" ht="16.5" spans="1:6">
-      <c r="A96" s="4" t="s">
-        <v>86</v>
+      <c r="A96" s="44">
+        <v>10</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>118</v>
@@ -6427,8 +6453,8 @@
       </c>
     </row>
     <row r="97" ht="16.5" spans="1:6">
-      <c r="A97" s="4" t="s">
-        <v>86</v>
+      <c r="A97" s="44">
+        <v>10</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>119</v>
@@ -6451,8 +6477,8 @@
       </c>
     </row>
     <row r="98" ht="16.5" spans="1:6">
-      <c r="A98" s="4" t="s">
-        <v>86</v>
+      <c r="A98" s="44">
+        <v>10</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>120</v>
@@ -6475,8 +6501,8 @@
       </c>
     </row>
     <row r="99" ht="16.5" spans="1:6">
-      <c r="A99" s="4" t="s">
-        <v>86</v>
+      <c r="A99" s="44">
+        <v>10</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>121</v>
